--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96078</v>
+        <v>96080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96080</v>
+        <v>96081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96108</v>
+        <v>96114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96114</v>
+        <v>96121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96121</v>
+        <v>96125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96125</v>
+        <v>96132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96135</v>
+        <v>96140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96140</v>
+        <v>96145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685494</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128685750</v>
       </c>
       <c r="B3" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -675,39 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685494</v>
+        <v>128685750</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -715,24 +711,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med groddkorn</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klövs skog, Solberga, Ög</t>
+          <t>Klövs skog, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540677</v>
+        <v>540636</v>
       </c>
       <c r="R2" t="n">
-        <v>6534920</v>
+        <v>6534924</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,35 +792,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685750</v>
+        <v>128685494</v>
       </c>
       <c r="B3" t="n">
-        <v>96158</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -837,19 +832,24 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med groddkorn</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klövs skog, Ög</t>
+          <t>Klövs skog, Solberga, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540636</v>
+        <v>540677</v>
       </c>
       <c r="R3" t="n">
-        <v>6534924</v>
+        <v>6534920</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58806-2022 artfynd.xlsx
+++ b/artfynd/A 58806-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128685750</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,8 +925,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128685494</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>